--- a/tame_output/ON/bt/strategyON_20241008.xlsx
+++ b/tame_output/ON/bt/strategyON_20241008.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>55.8%</t>
+          <t>55.4%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2106</v>
+        <v>2107</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,7 +628,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>18.0%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.6%</t>
+          <t>-11.3%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>54.0%</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>101.8%</t>
+          <t>101.6%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2106</v>
+        <v>2107</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>84.7%</t>
+          <t>84.6%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>147.1%</t>
+          <t>146.6%</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.3%</t>
+          <t>-78.2%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -931,11 +931,11 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.1%</t>
+          <t>52.2%</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2106</v>
+        <v>2107</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-74.8%</t>
+          <t>-74.7%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>423.9%</t>
+          <t>423.8%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-675.5%</t>
+          <t>-674.3%</t>
         </is>
       </c>
     </row>
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2106</v>
+        <v>2107</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>56.1%</t>
+          <t>56.0%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>12.7%</t>
+          <t>12.6%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-123.2%</t>
+          <t>-123.1%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-5.7%</t>
+          <t>-5.6%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2106</v>
+        <v>2107</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-6.4%</t>
+          <t>-6.2%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-112.9%</t>
+          <t>-112.3%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>109.6%</t>
+          <t>109.5%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2106</v>
+        <v>2107</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-9.1%</t>
+          <t>-9.2%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>99.0%</t>
+          <t>98.9%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2109"/>
+  <dimension ref="A1:G2110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -50052,7 +50052,7 @@
         <v>45571</v>
       </c>
       <c r="B2109" t="n">
-        <v>3.836620573654788</v>
+        <v>3.834420138157316</v>
       </c>
       <c r="C2109" t="n">
         <v>4.586977297831431</v>
@@ -50068,6 +50068,29 @@
       </c>
       <c r="G2109" t="n">
         <v>5.253660937357463</v>
+      </c>
+    </row>
+    <row r="2110">
+      <c r="A2110" s="2" t="n">
+        <v>45572</v>
+      </c>
+      <c r="B2110" t="n">
+        <v>3.82043457437072</v>
+      </c>
+      <c r="C2110" t="n">
+        <v>4.582427905253737</v>
+      </c>
+      <c r="D2110" t="n">
+        <v>-5.127552687714323</v>
+      </c>
+      <c r="E2110" t="n">
+        <v>2.53105040585426</v>
+      </c>
+      <c r="F2110" t="n">
+        <v>1.117370794401264</v>
+      </c>
+      <c r="G2110" t="n">
+        <v>5.252850381894495</v>
       </c>
     </row>
   </sheetData>
